--- a/backend/DB_table.xlsx
+++ b/backend/DB_table.xlsx
@@ -16,12 +16,1206 @@
     <x:sheet name="컬럼 상세 명세" sheetId="2" r:id="rId5"/>
     <x:sheet name="초기 데이터(Seed)" sheetId="3" r:id="rId6"/>
   </x:sheets>
+  <x:definedNames>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'초기 데이터(Seed)'!$A$1:$D$1</x:definedName>
+  </x:definedNames>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="581">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="581">
+  <x:si>
+    <x:t>AWS SysOps Administrator</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AWS_SYSOPS_ADMINISTRATOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>같은 분류 내 노출 순서, DEFAULT 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO_PROCESSING_ENGINEER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIG_DATA_ANALYST_ENGINEER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIQUE, 회의록 코드 (예: MTG-001)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예: feature/TASK-123-signup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENDING_APPROVAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>langsmith_trace_url</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사내 이메일/아이디, UNIQUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIQUE (예: DONE)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>user_certification</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y/N,  DEFAULT 'Y</x:t>
+  </x:si>
+  <x:si>
+    <x:t>assignment_reason</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회의록/기획서 등 원본 레코드 FK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>total_latency_ms</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPUTER_LITERACY_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Azure Fundamentals</x:t>
+  </x:si>
+  <x:si>
+    <x:t>status 실패/부분실패 시 사유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pull Request URL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>difficulty_reason</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FK, CommonCode.id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연동할 GitHub 저장소 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slack_webhook_url</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GitHub 연동 대상 식별자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZURE_FUNDAMENTALS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resignation_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>linked_pr_number</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Slack 알림 발송 대상 식별자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FK, MeetingNote.id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예: 회의요약→기획서 파이프라인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIQUE (예: STATUS)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIQUE (예: TASK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MeetingNote - 회의록</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPUTER_LITERACY_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEETING_TO_PROPOSAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROPOSAL_TO_REQSPEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>assigned_workload</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배분 반려 시 사유. 반려되면 status는 BACKLOG로 복귀 + assignee_id 해제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로젝트 알림 발송용 Slack 웹훅 주소 (연동 저장 API가 이미 있는 필드)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저장소 접근용 토큰 (암호화 저장 필요 — User.password와 같은 이유)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PK, 시스템 내부 식별자(UUID). 다른 테이블이 이 사람을 참조할 때 쓰는 값. 사람이 직접 볼 일은 거의 없음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최초 로그인 시 비밀번호 변경 강제 플래그</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LangSmith 최상위 Trace 딥링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEPUTY_GENERAL_MANAGER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AWS Developer Associate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>must_change_password</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AI 추천 당시 담당자 부하(%) 스냅샷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AWS_SOLUTIONS_ARCHITECT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO_SECURITY_ENGINEER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DB 명세서 - 테이블 목록 Summary</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AWS Solutions Architect</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETWORK_ADMINISTRATOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AWS_DEVELOPER_ASSOCIATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FK, User.id, 배전전엔 null</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면에서 선택 안하면 비어 있을 수 있음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과거 참여 프로젝트 이력. AI 담당자 추천 시 "유사경험(experienceFit)" 판단 근거로 실제 사용됨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소분류 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESIGN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핸드폰번호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직원자격증</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비밀번호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AI히스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자격증 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>null</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로젝트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PyTorch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료 예정일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로젝트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>note</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회의 제목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직원기술</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정렬 순서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사원번호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생성일시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_yn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수정일시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>email</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회의 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHAR(1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기획서 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최근 로그인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코드 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작 시각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디자인팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGINT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QA_TEAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대상 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대상 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 상태</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기획서 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기획서 제목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반려사유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>업무배분 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완료 시각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLOAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>task_no</x:t>
+  </x:si>
+  <x:si>
+    <x:t>status</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최초 작성일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실행 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오류 메시지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>업무 시작일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반려 사유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIGMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원본 링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REQSPEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최초 생성일시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Express</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회의록 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOTNET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Spring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUNNING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prisma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부분실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Django</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NestJS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKILL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NODEJS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Backend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이프라인명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FASTAPI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HISTORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACTIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAILED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>승인된 시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배정 근거</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUCCESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Node.js</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GraphQL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Docker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRISMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DJANGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>.NET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAPHQL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SPRING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEXTJS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANDROID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Angular</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CI_CD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rust</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGULAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jira</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLUTTER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NESTJS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CSHARP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADMIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZURE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYTHON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Android</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKETCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sketch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTML</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FastAPI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOCKED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGILE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTLIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUST</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리눅스마스터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GTQi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필수여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADSP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정보보안기사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Next.js</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADsP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CISSP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GTQI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Java</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Python</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCRUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kotlin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEST</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Azure</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBILE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테이블 물리명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REACT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Flutter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CYPRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CI/CD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중분류 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETWORK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정보처리기사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네트워크관리사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SQLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>React</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATA_AI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대분류 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BACKLOG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테이블명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MySQL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDIUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFFICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>채번용 순번</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배분승인대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR리뷰중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Linux</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OCJP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JEST</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데이터 타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>content</x:t>
+  </x:si>
+  <x:si>
+    <x:t>컬럼 한글명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERGED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행 중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공통코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>컬럼 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cypress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TASK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENDING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MONGODB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HIGH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DRAFT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SQLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REDIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마케팅팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>승인자 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MongoDB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>req_no</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PANDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기획서 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cert_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결 브랜치명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예상 소요시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MYSQL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계정 생성일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직원 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>승인대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOOLEAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Figma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HR_TEAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SENIOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVOPS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>승인완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로젝트 제목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작성자 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마지막 수정일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>승인일시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAGER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>난이도판단근거</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEXT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>user_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>담당자 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINUX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DevOps</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BACKEND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회의 일시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회의 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기획서 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYTORCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>history</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요구사항정의서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>task</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STAFF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pandas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로젝트 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회의록 본문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>업무배분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>user</x:t>
+  </x:si>
+  <x:si>
+    <x:t>req_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>project</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참석자명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실제 완료일시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENERAL_MANAGER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요구사항정의서→업무(WBS)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요구사항정의서 내부 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UI/UX Designer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>meeting_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLOUD_DEVOPS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>reject_reason</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLANNING_TEAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARTIAL_FAILED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>업무에 대한 상세 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESIGN_SYSTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VARCHAR(100)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REQSPEC_TO_TASK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pull Request 번호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VARCHAR(500)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>completed_at</x:t>
+  </x:si>
+  <x:si>
+    <x:t>last_login_at</x:t>
+  </x:si>
+  <x:si>
+    <x:t>github_owner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비밀번호 변경 필요 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VARCHAR(200)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>\tSlack 웹훅 URL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pipeline_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIQUE, 사원번호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VARCHAR(300)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VARCHAR(255)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_code_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>github_token</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예: 회원가입 API 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FK, ReqSpec.id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실제 회의가 시작된 시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FK, Project.id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>linked_pr_url</x:t>
+  </x:si>
+  <x:si>
+    <x:t>총 테이블 수: 10개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>meeting_no 생성용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테이블 논리명(한글명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>meeting_note</x:t>
+  </x:si>
+  <x:si>
+    <x:t>project_no 생성용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENDING_REVIEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>total_tokens</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조직 관리에 필요할 경우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>past_projects</x:t>
+  </x:si>
+  <x:si>
+    <x:t>error_message</x:t>
+  </x:si>
+  <x:si>
+    <x:t>github_email</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOFTWARE_DEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINUX_MASTER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAILWIND_CSS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tailwind CSS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UIUX_DESIGNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIPELINE_NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROJECT_MANAGER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Project Manager</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATA_ANALYSIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKETING_TEAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEETING_NOTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CERTIFICATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>React Native</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REACT_NATIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATA_ENGINEER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data Engineer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Design System</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FK, Proposal.id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실행중/성공/실패/부분실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>estimated_hours</x:t>
+  </x:si>
+  <x:si>
+    <x:t>planning_no 생성용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0~100(%), 기본값 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기획서에 대한 간단한 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>linked_branch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>triggered_by</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data Analysis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DECIMAL(5,2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO_PROCESSING_INDUSTRIAL_ENGINEER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO_SECURITY_INDUSTRIAL_ENGINEER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퇴사일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Git</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개발팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QA팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>seq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GTQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기획팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기획서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No</x:t>
+  </x:si>
+  <x:si>
+    <x:t>컬럼명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코드명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한글명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>활성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인사팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y</x:t>
+  </x:si>
+  <x:si>
+    <x:t>입사일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CSS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영업팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수정일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>등록일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C#</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SQL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>관리자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AWS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직원</x:t>
+  </x:si>
   <x:si>
     <x:t>낮음</x:t>
   </x:si>
@@ -32,345 +1226,144 @@
     <x:t>미연동</x:t>
   </x:si>
   <x:si>
-    <x:t>관리자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AWS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직원</x:t>
+    <x:t>부장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>팀장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회의록</x:t>
+  </x:si>
+  <x:si>
+    <x:t>차장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VCS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PMP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Go</x:t>
+  </x:si>
+  <x:si>
+    <x:t>높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실행중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반려</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퇴사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
   </x:si>
   <x:si>
     <x:t>완료</x:t>
   </x:si>
   <x:si>
-    <x:t>퇴사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실행중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>차장</x:t>
+    <x:t>보통</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>취소됨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>API</x:t>
   </x:si>
   <x:si>
     <x:t>진행률</x:t>
   </x:si>
   <x:si>
-    <x:t>보통</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>팀장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>취소됨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반려</x:t>
-  </x:si>
-  <x:si>
-    <x:t>API</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회의록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ITQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VCS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PM</x:t>
-  </x:si>
-  <x:si>
     <x:t>iOS</x:t>
   </x:si>
   <x:si>
     <x:t>업무명</x:t>
   </x:si>
   <x:si>
-    <x:t>PMP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Go</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>No</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>seq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>입사일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>컬럼명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Git</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퇴사일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한글명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GTQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기획서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QA_TEAM</x:t>
+    <x:t>실제 요구사항 본문</x:t>
   </x:si>
   <x:si>
     <x:t>VARCHAR(50)</x:t>
   </x:si>
   <x:si>
+    <x:t>최종 수정 일시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 표시용 한글명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>employee_no</x:t>
+  </x:si>
+  <x:si>
+    <x:t>updated_at</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEAM_LEAD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATETIME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>github_repo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>large_code</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sort_order</x:t>
+  </x:si>
+  <x:si>
+    <x:t>medium_code</x:t>
+  </x:si>
+  <x:si>
     <x:t>code_name</x:t>
   </x:si>
   <x:si>
-    <x:t>화면 표시용 한글명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>medium_code</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATETIME</x:t>
-  </x:si>
-  <x:si>
     <x:t>created_at</x:t>
   </x:si>
   <x:si>
-    <x:t>sort_order</x:t>
-  </x:si>
-  <x:si>
-    <x:t>updated_at</x:t>
-  </x:si>
-  <x:si>
-    <x:t>employee_no</x:t>
-  </x:si>
-  <x:si>
-    <x:t>github_repo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEAM_LEAD</x:t>
-  </x:si>
-  <x:si>
     <x:t>small_code</x:t>
   </x:si>
   <x:si>
-    <x:t>large_code</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최종 수정 일시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최초 로그인 시 비밀번호 변경 강제 플래그</x:t>
-  </x:si>
-  <x:si>
-    <x:t>must_change_password</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FK, User.id, 배전전엔 null</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DB 명세서 - 테이블 목록 Summary</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AWS Solutions Architect</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETWORK_ADMINISTRATOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO_SECURITY_ENGINEER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AI 추천 당시 담당자 부하(%) 스냅샷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AWS_SOLUTIONS_ARCHITECT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LangSmith 최상위 Trace 딥링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AWS_DEVELOPER_ASSOCIATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AWS Developer Associate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면에서 선택 안하면 비어 있을 수 있음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEPUTY_GENERAL_MANAGER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>task_no</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIGMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원본 링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완료 시각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>업무배분 코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체 상태</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최초 작성일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반려사유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오류 메시지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLOAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>업무 시작일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대상 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>status</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGINT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작 시각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반려 사유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디자인팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대상 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기획서 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기획서 제목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실행 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배정 근거</x:t>
-  </x:si>
-  <x:si>
-    <x:t>승인된 시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회의록 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최초 생성일시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Backend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이프라인명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실제 요구사항 본문</x:t>
+    <x:t>연동할 GitHub 저장소의 소유자(조직/사용자명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCP_ASSOCIATE_CLOUD_ENGINEER</x:t>
   </x:si>
   <x:si>
     <x:t>UNIQUE, 기획서 번호 , (예: PLN-001)</x:t>
   </x:si>
   <x:si>
-    <x:t>연동할 GitHub 저장소의 소유자(조직/사용자명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCP_ASSOCIATE_CLOUD_ENGINEER</x:t>
-  </x:si>
-  <x:si>
     <x:t>GCP Associate Cloud Engineer</x:t>
   </x:si>
   <x:si>
@@ -383,484 +1376,10 @@
     <x:t>UNIQUE, 사람이 보는 코드 (예: PRJ-001)</x:t>
   </x:si>
   <x:si>
-    <x:t>EXPRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKILL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Django</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FASTAPI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부분실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACTIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NestJS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOTNET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUCCESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HISTORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Spring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REQSPEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NODEJS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAILED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUNNING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prisma</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Express</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Node.js</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GraphQL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DJANGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOCKED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADMIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>.NET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LEAVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAPHQL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SPRING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FastAPI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRISMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Docker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NESTJS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CSHARP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANDROID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGILE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGULAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rust</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZURE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEXTJS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Android</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Jira</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKETCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYTHON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JAVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLUTTER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sketch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTML</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTLIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Angular</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CI_CD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>React</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Agile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBILE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Flutter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CI/CD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Next.js</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kotlin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Python</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Azure</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Java</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REACT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCRUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필수여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중분류 코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테이블 물리명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADsP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리눅스마스터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CYPRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GTQI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GTQi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADSP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정보보안기사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CISSP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정보처리기사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETWORK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네트워크관리사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SQLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>컬럼 한글명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Jest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SQLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JEST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OCJP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공통코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFFICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cypress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데이터 타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>content</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대분류 코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>컬럼 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERGED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테이블명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PR리뷰중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redis</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATA_AI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Linux</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TASK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행 중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>채번용 순번</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BACKLOG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REDIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENDING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MONGODB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HIGH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배분승인대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MySQL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DRAFT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDIUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MongoDB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>승인대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Figma</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MYSQL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINUX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PANDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>승인완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AWS SysOps Administrator</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIQUE, 회의록 코드 (예: MTG-001)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>같은 분류 내 노출 순서, DEFAULT 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO_PROCESSING_ENGINEER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AWS_SYSOPS_ADMINISTRATOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예: feature/TASK-123-signup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIG_DATA_ANALYST_ENGINEER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연동할 GitHub 저장소 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Slack 알림 발송 대상 식별자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resignation_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회의록/기획서 등 원본 레코드 FK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사내 이메일/아이디, UNIQUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIQUE (예: STATUS)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예: 회의요약→기획서 파이프라인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>user_certification</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIQUE (예: DONE)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GitHub 연동 대상 식별자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIQUE (예: TASK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>difficulty_reason</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pull Request URL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>linked_pr_number</x:t>
-  </x:si>
-  <x:si>
-    <x:t>assignment_reason</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FK, MeetingNote.id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FK, CommonCode.id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENDING_APPROVAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y/N,  DEFAULT 'Y</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slack_webhook_url</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MeetingNote - 회의록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>total_latency_ms</x:t>
-  </x:si>
-  <x:si>
-    <x:t>langsmith_trace_url</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Azure Fundamentals</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZURE_FUNDAMENTALS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPUTER_LITERACY_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>status 실패/부분실패 시 사유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPUTER_LITERACY_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEETING_TO_PROPOSAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROPOSAL_TO_REQSPEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>assigned_workload</x:t>
+    <x:t>실행중이면 null</x:t>
+  </x:si>
+  <x:si>
+    <x:t>총 토큰 사용량</x:t>
   </x:si>
   <x:si>
     <x:t>VARCHAR(30)</x:t>
@@ -872,9 +1391,6 @@
     <x:t>entity_id</x:t>
   </x:si>
   <x:si>
-    <x:t>실행중이면 null</x:t>
-  </x:si>
-  <x:si>
     <x:t>entity_type</x:t>
   </x:si>
   <x:si>
@@ -884,883 +1400,370 @@
     <x:t>완료 시에만 계산</x:t>
   </x:si>
   <x:si>
-    <x:t>총 토큰 사용량</x:t>
-  </x:si>
-  <x:si>
     <x:t>업무 종료 예정일</x:t>
   </x:si>
   <x:si>
+    <x:t>JavaScript</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RESIGNED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>started_at</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAVASCRIPT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기획서→요구사항정의서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>progress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회의요약→기획서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTITY_TYPE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REST_API</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결 PR 링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROPOSAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실행 트리거 사용자</x:t>
+  </x:si>
+  <x:si>
     <x:t>배정 시점 부하율</x:t>
   </x:si>
   <x:si>
-    <x:t>연결 PR 링크</x:t>
-  </x:si>
-  <x:si>
     <x:t>task_no 생성용</x:t>
   </x:si>
   <x:si>
-    <x:t>실행 트리거 사용자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>progress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>started_at</x:t>
-  </x:si>
-  <x:si>
     <x:t>연결 PR 번호</x:t>
   </x:si>
   <x:si>
     <x:t>하위 노드 합산</x:t>
   </x:si>
   <x:si>
-    <x:t>JAVASCRIPT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기획서→요구사항정의서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROPOSAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JavaScript</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RESIGNED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회의요약→기획서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTITY_TYPE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REST_API</x:t>
+    <x:t>Illustrator</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTOTYPING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TensorFlow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERRAFORM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POSTGRESQL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LANGUAGE</x:t>
   </x:si>
   <x:si>
     <x:t>TENSORFLOW</x:t>
   </x:si>
   <x:si>
-    <x:t>TERRAFORM</x:t>
+    <x:t>UX Research</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ILLUSTRATOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REST API</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PostgreSQL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATABASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUBERNETES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHOTOSHOP</x:t>
   </x:si>
   <x:si>
     <x:t>Terraform</x:t>
   </x:si>
   <x:si>
-    <x:t>TensorFlow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ILLUSTRATOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Illustrator</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PostgreSQL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POSTGRESQL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REST API</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTOTYPING</x:t>
-  </x:si>
-  <x:si>
     <x:t>Kubernetes</x:t>
   </x:si>
   <x:si>
-    <x:t>DATABASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UX Research</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUBERNETES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHOTOSHOP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LANGUAGE</x:t>
+    <x:t>프로젝트 종료 예정일</x:t>
   </x:si>
   <x:si>
     <x:t>TypeScript</x:t>
   </x:si>
   <x:si>
+    <x:t>Prototyping</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UX_RESEARCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>end_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>author_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GitHub 이메일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반드시 해시하여 저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과거 프로젝트 이력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slack_email</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계정 정보 수정일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로젝트 생성자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Photoshop</x:t>
+  </x:si>
+  <x:si>
+    <x:t>password</x:t>
+  </x:si>
+  <x:si>
     <x:t>TYPESCRIPT</x:t>
   </x:si>
   <x:si>
-    <x:t>Photoshop</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UX_RESEARCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prototyping</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slack_email</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계정 정보 수정일</x:t>
-  </x:si>
-  <x:si>
     <x:t>마지막 로그인 시간</x:t>
   </x:si>
   <x:si>
-    <x:t>GitHub 이메일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과거 프로젝트 이력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트 종료 예정일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반드시 해시하여 저장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>password</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트 생성자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>end_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t>author_id</x:t>
+    <x:t>project_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로젝트 시작일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로젝트 상세 설명</x:t>
   </x:si>
   <x:si>
     <x:t>project_no</x:t>
   </x:si>
   <x:si>
+    <x:t>description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>start_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>approved_by</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기획서 내부 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>participant</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회의록 내부 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Slack 이메일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로젝트 내부 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GitHub 저장소명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GitHub 소유자</x:t>
+  </x:si>
+  <x:si>
     <x:t>FK, User.id</x:t>
   </x:si>
   <x:si>
     <x:t>기술 코드 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>프로젝트 상세 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>start_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Slack 이메일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GitHub 소유자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트 내부 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트 시작일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회의록 내부 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>approved_by</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GitHub 저장소명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>project_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기획서 내부 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>participant</x:t>
+    <x:t>기획서 반려사유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>assignee_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>approved_at</x:t>
   </x:si>
   <x:si>
     <x:t>요구사항정의서 번호</x:t>
   </x:si>
   <x:si>
+    <x:t>planning_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실제 기획서 본문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VARCHAR(20)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hire_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회사 이메일/아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>meeting_no</x:t>
+  </x:si>
+  <x:si>
+    <x:t>meeting_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEV_TEAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>planning_no</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEXT(JSON)</x:t>
+  </x:si>
+  <x:si>
     <x:t>GitHub 토큰</x:t>
   </x:si>
   <x:si>
-    <x:t>meeting_no</x:t>
-  </x:si>
-  <x:si>
-    <x:t>meeting_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>planning_no</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hire_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t>planning_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실제 기획서 본문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VARCHAR(20)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회사 이메일/아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>approved_at</x:t>
-  </x:si>
-  <x:si>
     <x:t>LONGTEXT</x:t>
   </x:si>
   <x:si>
-    <x:t>기획서 반려사유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEXT(JSON)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>assignee_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEV_TEAM</x:t>
+    <x:t>업무 상세 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESIGN_TEAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>업무배분 내부 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>req_no 생성용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요구사항정의서 수정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEPARTMENT</x:t>
   </x:si>
   <x:si>
     <x:t>JOB_ROLE</x:t>
   </x:si>
   <x:si>
-    <x:t>DEPARTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>업무 상세 설명</x:t>
-  </x:si>
-  <x:si>
     <x:t>난이도 판단 근거</x:t>
   </x:si>
   <x:si>
-    <x:t>요구사항정의서 수정</x:t>
+    <x:t>요구사항정의서 ID</x:t>
   </x:si>
   <x:si>
     <x:t>SALES_TEAM</x:t>
   </x:si>
   <x:si>
-    <x:t>req_no 생성용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESIGN_TEAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>업무배분 내부 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요구사항정의서 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DevOps</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BACKEND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVOPS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SENIOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마케팅팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAGER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HR_TEAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코드명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영업팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기획팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>활성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CSS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>개발팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인사팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QA팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수정일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SQL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C#</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>등록일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배분 반려 시 사유. 반려되면 status는 BACKLOG로 복귀 + assignee_id 해제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트 알림 발송용 Slack 웹훅 주소 (연동 저장 API가 이미 있는 필드)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저장소 접근용 토큰 (암호화 저장 필요 — User.password와 같은 이유)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PK, 시스템 내부 식별자(UUID). 다른 테이블이 이 사람을 참조할 때 쓰는 값. 사람이 직접 볼 일은 거의 없음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과거 참여 프로젝트 이력. AI 담당자 추천 시 "유사경험(experienceFit)" 판단 근거로 실제 사용됨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트 제목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계정 생성일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직원 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작성자 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마지막 수정일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>승인자 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOOLEAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cert_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>승인일시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기획서 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>난이도판단근거</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEXT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>user_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>req_no</x:t>
-  </x:si>
-  <x:si>
-    <x:t>담당자 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연결 브랜치명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예상 소요시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회의 일시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>req_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기획서 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYTORCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STAFF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pandas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회의 코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트 코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실제 완료일시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>project</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회의록 본문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요구사항정의서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>history</x:t>
-  </x:si>
-  <x:si>
-    <x:t>task</x:t>
-  </x:si>
-  <x:si>
-    <x:t>user</x:t>
-  </x:si>
-  <x:si>
-    <x:t>업무배분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참석자명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PyTorch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직원기술</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핸드폰번호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESIGN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AI히스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직원자격증</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최근 로그인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소분류 코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>note</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정렬 순서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>null</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코드 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로젝트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_yn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자격증 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>email</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회의 제목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비밀번호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수정일시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHAR(1)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사원번호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생성일시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회의 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료 예정일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기획서 코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>phone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO_PROCESSING_INDUSTRIAL_ENGINEER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO_SECURITY_INDUSTRIAL_ENGINEER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOFTWARE_DEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CERTIFICATION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATA_ENGINEER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data Engineer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKETING_TEAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEETING_NOTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINUX_MASTER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>React Native</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REACT_NATIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAILWIND_CSS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tailwind CSS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UIUX_DESIGNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIPELINE_NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROJECT_MANAGER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Project Manager</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATA_ANALYSIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>planning_no 생성용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>estimated_hours</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0~100(%), 기본값 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DECIMAL(5,2)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기획서에 대한 간단한 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>linked_branch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>triggered_by</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data Analysis</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FK, Proposal.id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Design System</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실행중/성공/실패/부분실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요구사항정의서→업무(WBS)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLOUD_DEVOPS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요구사항정의서 내부 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>reject_reason</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENERAL_MANAGER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UI/UX Designer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>meeting_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESIGN_SYSTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PLANNING_TEAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>업무에 대한 상세 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL_FAILED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FK, ReqSpec.id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예: 회원가입 API 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실제 회의가 시작된 시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REQSPEC_TO_TASK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>meeting_no 생성용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pull Request 번호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VARCHAR(500)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>pipeline_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VARCHAR(255)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VARCHAR(100)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIQUE, 사원번호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테이블 논리명(한글명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FK, Project.id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>github_owner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>meeting_note</x:t>
-  </x:si>
-  <x:si>
-    <x:t>completed_at</x:t>
-  </x:si>
-  <x:si>
-    <x:t>total_tokens</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조직 관리에 필요할 경우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>last_login_at</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비밀번호 변경 필요 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VARCHAR(200)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>project_no 생성용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>\tSlack 웹훅 URL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VARCHAR(300)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>linked_pr_url</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_code_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>past_projects</x:t>
-  </x:si>
-  <x:si>
-    <x:t>github_token</x:t>
-  </x:si>
-  <x:si>
-    <x:t>총 테이블 수: 10개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENDING_REVIEW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>error_message</x:t>
-  </x:si>
-  <x:si>
-    <x:t>github_email</x:t>
+    <x:t>req_spec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공통 코드 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QA_ENGINEER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRECTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>user_skill</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHAR(36)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PK, UUID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPLOYEE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Full-stack</x:t>
   </x:si>
   <x:si>
     <x:t>QA Engineer</x:t>
   </x:si>
   <x:si>
+    <x:t>FULLSTACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRONTEND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POSITION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Frontend</x:t>
+  </x:si>
+  <x:si>
     <x:t>ASSISTANT</x:t>
   </x:si>
   <x:si>
-    <x:t>EMPLOYEE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POSITION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>user_skill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PK, UUID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QA_ENGINEER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공통 코드 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHAR(36)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIRECTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Full-stack</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLSTACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRONTEND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Frontend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>req_spec</x:t>
+    <x:t>IN_PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>APPROVED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIFFICULTY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELENIUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>컴퓨터활용능력 1급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>common_code</x:t>
+  </x:si>
+  <x:si>
+    <x:t>컴퓨터활용능력 2급</x:t>
   </x:si>
   <x:si>
     <x:t>proposal</x:t>
   </x:si>
   <x:si>
-    <x:t>common_code</x:t>
+    <x:t>Selenium</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정보처리산업기사</x:t>
   </x:si>
   <x:si>
     <x:t>SECURITY</x:t>
   </x:si>
   <x:si>
-    <x:t>SELENIUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정보처리산업기사</x:t>
+    <x:t>IN_REVIEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빅데이터분석기사</x:t>
   </x:si>
   <x:si>
     <x:t>정보보안산업기사</x:t>
   </x:si>
   <x:si>
-    <x:t>빅데이터분석기사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>컴퓨터활용능력 1급</x:t>
-  </x:si>
-  <x:si>
-    <x:t>컴퓨터활용능력 2급</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selenium</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN_REVIEW</x:t>
-  </x:si>
-  <x:si>
     <x:t>REJECTED</x:t>
   </x:si>
   <x:si>
-    <x:t>APPROVED</x:t>
-  </x:si>
-  <x:si>
     <x:t>GIT_STATUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN_PROGRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIFFICULTY</x:t>
   </x:si>
   <x:si>
     <x:t>CANCELLED</x:t>
@@ -2242,26 +2245,26 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="20.64999999999999857891">
       <x:c r="A1" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="2" t="s">
-        <x:v>545</x:v>
+        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>528</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>214</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
@@ -2269,10 +2272,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D5" s="4">
         <x:v>10</x:v>
@@ -2283,10 +2286,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="D6" s="4">
         <x:v>15</x:v>
@@ -2300,7 +2303,7 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>447</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D7" s="4">
         <x:v>3</x:v>
@@ -2311,10 +2314,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>256</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>452</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D8" s="4">
         <x:v>2</x:v>
@@ -2325,10 +2328,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D9" s="4">
         <x:v>15</x:v>
@@ -2339,10 +2342,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C10" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="D10" s="4">
         <x:v>13</x:v>
@@ -2353,10 +2356,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="C11" s="6" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D11" s="4">
         <x:v>14</x:v>
@@ -2367,10 +2370,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>563</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>440</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D12" s="4">
         <x:v>9</x:v>
@@ -2381,10 +2384,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C13" s="6" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D13" s="4">
         <x:v>21</x:v>
@@ -2395,10 +2398,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D14" s="4">
         <x:v>13</x:v>
@@ -2428,600 +2431,600 @@
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="3" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="s">
-        <x:v>203</x:v>
-      </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="F1" s="3" t="s">
-        <x:v>184</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G1" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>359</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="5" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B2" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C2" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="D2" s="7" t="s">
-        <x:v>556</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="E2" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F2" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G2" s="7" t="s">
-        <x:v>554</x:v>
+        <x:v>555</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="5" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B3" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
-        <x:v>69</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>213</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E3" s="8" t="s">
-        <x:v>57</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="F3" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>259</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="5" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>60</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>185</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E4" s="8" t="s">
-        <x:v>57</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="F4" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>254</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="5" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>68</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>455</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E5" s="8" t="s">
-        <x:v>57</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="F5" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G5" s="7" t="s">
-        <x:v>257</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="5" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>58</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>459</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E6" s="8" t="s">
-        <x:v>526</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F6" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G6" s="7" t="s">
-        <x:v>59</x:v>
+        <x:v>431</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="5" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>456</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>29</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="E7" s="8" t="s">
-        <x:v>523</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="F7" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G7" s="7" t="s">
-        <x:v>458</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="5" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>457</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E8" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F8" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G8" s="7" t="s">
-        <x:v>244</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="5" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>462</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
-        <x:v>460</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E9" s="8" t="s">
-        <x:v>468</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F9" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G9" s="7" t="s">
-        <x:v>267</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="5" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B10" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D10" s="7" t="s">
-        <x:v>470</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E10" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F10" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G10" s="7" t="s">
-        <x:v>470</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="5" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>64</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>467</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E11" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F11" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G11" s="7" t="s">
-        <x:v>70</x:v>
+        <x:v>430</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B12" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C12" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="D12" s="7" t="s">
-        <x:v>472</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E12" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F12" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G12" s="7" t="s">
-        <x:v>409</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B13" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C13" s="7" t="s">
-        <x:v>65</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="D13" s="7" t="s">
-        <x:v>469</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E13" s="8" t="s">
-        <x:v>526</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F13" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G13" s="7" t="s">
-        <x:v>527</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>464</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D14" s="7" t="s">
-        <x:v>362</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="E14" s="8" t="s">
-        <x:v>525</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F14" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G14" s="7" t="s">
-        <x:v>253</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B15" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>333</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="D15" s="7" t="s">
-        <x:v>466</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E15" s="8" t="s">
-        <x:v>525</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F15" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G15" s="7" t="s">
-        <x:v>332</x:v>
+        <x:v>498</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C16" s="7" t="s">
-        <x:v>474</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D16" s="7" t="s">
-        <x:v>41</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="E16" s="8" t="s">
-        <x:v>57</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="F16" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G16" s="7" t="s">
-        <x:v>413</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B17" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C17" s="7" t="s">
-        <x:v>476</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D17" s="7" t="s">
-        <x:v>44</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="E17" s="8" t="s">
-        <x:v>361</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F17" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G17" s="7" t="s">
-        <x:v>449</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B18" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C18" s="7" t="s">
-        <x:v>358</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="D18" s="7" t="s">
-        <x:v>46</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="E18" s="8" t="s">
-        <x:v>454</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F18" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G18" s="7" t="s">
-        <x:v>534</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B19" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C19" s="7" t="s">
-        <x:v>251</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D19" s="7" t="s">
-        <x:v>51</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="E19" s="8" t="s">
-        <x:v>454</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F19" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G19" s="7" t="s">
-        <x:v>51</x:v>
+        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B20" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C20" s="7" t="s">
-        <x:v>535</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="D20" s="7" t="s">
-        <x:v>453</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E20" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F20" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G20" s="7" t="s">
-        <x:v>328</x:v>
+        <x:v>506</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B21" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C21" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D21" s="7" t="s">
-        <x:v>412</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F21" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G21" s="7" t="s">
-        <x:v>470</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B22" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C22" s="7" t="s">
-        <x:v>64</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="D22" s="7" t="s">
-        <x:v>327</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="E22" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F22" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G22" s="7" t="s">
-        <x:v>467</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B23" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C23" s="7" t="s">
-        <x:v>72</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D23" s="7" t="s">
-        <x:v>536</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E23" s="8" t="s">
-        <x:v>417</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="F23" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G23" s="7" t="s">
-        <x:v>71</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B24" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C24" s="7" t="s">
-        <x:v>543</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="D24" s="7" t="s">
-        <x:v>330</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E24" s="8" t="s">
-        <x:v>422</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F24" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G24" s="7" t="s">
-        <x:v>410</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B25" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C25" s="7" t="s">
-        <x:v>326</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D25" s="7" t="s">
-        <x:v>343</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="E25" s="8" t="s">
-        <x:v>525</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F25" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G25" s="7" t="s">
-        <x:v>250</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="5" t="s">
-        <x:v>443</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B26" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C26" s="7" t="s">
-        <x:v>548</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="D26" s="7" t="s">
-        <x:v>329</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="E26" s="8" t="s">
-        <x:v>525</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F26" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G26" s="7" t="s">
-        <x:v>258</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
@@ -3029,22 +3032,22 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="B27" s="7" t="s">
-        <x:v>447</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C27" s="7" t="s">
-        <x:v>423</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D27" s="7" t="s">
-        <x:v>469</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E27" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F27" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G27" s="7" t="s">
-        <x:v>338</x:v>
+        <x:v>521</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
@@ -3052,22 +3055,22 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="B28" s="7" t="s">
-        <x:v>447</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C28" s="7" t="s">
-        <x:v>542</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="D28" s="7" t="s">
-        <x:v>339</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="E28" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F28" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G28" s="7" t="s">
-        <x:v>265</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
@@ -3075,2023 +3078,2023 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="B29" s="7" t="s">
-        <x:v>447</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C29" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D29" s="7" t="s">
-        <x:v>470</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E29" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F29" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G29" s="7" t="s">
-        <x:v>470</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="5" t="s">
-        <x:v>256</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B30" s="7" t="s">
-        <x:v>452</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C30" s="7" t="s">
-        <x:v>423</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D30" s="7" t="s">
-        <x:v>472</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E30" s="8" t="s">
-        <x:v>526</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F30" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G30" s="7" t="s">
-        <x:v>338</x:v>
+        <x:v>521</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="5" t="s">
-        <x:v>256</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B31" s="7" t="s">
-        <x:v>452</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C31" s="7" t="s">
-        <x:v>418</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="D31" s="7" t="s">
-        <x:v>463</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E31" s="8" t="s">
-        <x:v>526</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F31" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G31" s="7" t="s">
-        <x:v>265</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B32" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C32" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="D32" s="7" t="s">
-        <x:v>345</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="E32" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F32" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G32" s="7" t="s">
-        <x:v>409</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B33" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C33" s="7" t="s">
-        <x:v>337</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="D33" s="7" t="s">
-        <x:v>435</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E33" s="8" t="s">
-        <x:v>361</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F33" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G33" s="7" t="s">
-        <x:v>119</x:v>
+        <x:v>449</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B34" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C34" s="7" t="s">
-        <x:v>336</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D34" s="7" t="s">
-        <x:v>334</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="E34" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F34" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G34" s="7" t="s">
-        <x:v>338</x:v>
+        <x:v>521</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B35" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C35" s="7" t="s">
-        <x:v>439</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D35" s="7" t="s">
-        <x:v>411</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E35" s="8" t="s">
-        <x:v>537</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F35" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G35" s="7" t="s">
-        <x:v>411</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B36" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C36" s="7" t="s">
-        <x:v>341</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="D36" s="7" t="s">
-        <x:v>340</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="E36" s="8" t="s">
-        <x:v>422</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F36" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G36" s="7" t="s">
-        <x:v>340</x:v>
+        <x:v>509</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B37" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C37" s="7" t="s">
-        <x:v>342</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D37" s="7" t="s">
-        <x:v>40</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E37" s="8" t="s">
-        <x:v>454</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F37" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G37" s="7" t="s">
-        <x:v>346</x:v>
+        <x:v>508</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B38" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C38" s="7" t="s">
-        <x:v>335</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="D38" s="7" t="s">
-        <x:v>473</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E38" s="8" t="s">
-        <x:v>454</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F38" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G38" s="7" t="s">
-        <x:v>331</x:v>
+        <x:v>491</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B39" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C39" s="7" t="s">
-        <x:v>532</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D39" s="7" t="s">
-        <x:v>436</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="E39" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F39" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G39" s="7" t="s">
-        <x:v>436</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B40" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C40" s="7" t="s">
-        <x:v>268</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D40" s="7" t="s">
-        <x:v>539</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E40" s="8" t="s">
-        <x:v>525</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F40" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G40" s="7" t="s">
-        <x:v>407</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B41" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C41" s="7" t="s">
-        <x:v>530</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="D41" s="7" t="s">
-        <x:v>344</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="E41" s="8" t="s">
-        <x:v>526</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F41" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G41" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>443</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B42" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C42" s="7" t="s">
-        <x:v>66</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="D42" s="7" t="s">
-        <x:v>349</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="E42" s="8" t="s">
-        <x:v>526</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F42" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G42" s="7" t="s">
-        <x:v>249</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B43" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C43" s="7" t="s">
-        <x:v>544</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="D43" s="7" t="s">
-        <x:v>354</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="E43" s="8" t="s">
-        <x:v>525</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F43" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G43" s="7" t="s">
-        <x:v>408</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B44" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C44" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D44" s="7" t="s">
-        <x:v>470</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E44" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F44" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G44" s="7" t="s">
-        <x:v>470</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B45" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C45" s="7" t="s">
-        <x:v>64</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="D45" s="7" t="s">
-        <x:v>467</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E45" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F45" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G45" s="7" t="s">
-        <x:v>467</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="5" t="s">
-        <x:v>437</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B46" s="7" t="s">
-        <x:v>448</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C46" s="7" t="s">
-        <x:v>43</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D46" s="7" t="s">
-        <x:v>223</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E46" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F46" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G46" s="7" t="s">
-        <x:v>538</x:v>
+        <x:v>317</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B47" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C47" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="D47" s="7" t="s">
-        <x:v>347</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="E47" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F47" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G47" s="7" t="s">
-        <x:v>409</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B48" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C48" s="7" t="s">
-        <x:v>355</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="D48" s="7" t="s">
-        <x:v>434</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E48" s="8" t="s">
-        <x:v>361</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F48" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G48" s="7" t="s">
-        <x:v>243</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B49" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C49" s="7" t="s">
-        <x:v>350</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="D49" s="7" t="s">
-        <x:v>461</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E49" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F49" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G49" s="7" t="s">
-        <x:v>529</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B50" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C50" s="7" t="s">
-        <x:v>336</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D50" s="7" t="s">
-        <x:v>414</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E50" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F50" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G50" s="7" t="s">
-        <x:v>338</x:v>
+        <x:v>521</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B51" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C51" s="7" t="s">
-        <x:v>342</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D51" s="7" t="s">
-        <x:v>40</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E51" s="8" t="s">
-        <x:v>454</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F51" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G51" s="7" t="s">
-        <x:v>346</x:v>
+        <x:v>508</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B52" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C52" s="7" t="s">
-        <x:v>335</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="D52" s="7" t="s">
-        <x:v>473</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E52" s="8" t="s">
-        <x:v>454</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F52" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G52" s="7" t="s">
-        <x:v>331</x:v>
+        <x:v>491</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B53" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C53" s="7" t="s">
-        <x:v>439</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D53" s="7" t="s">
-        <x:v>465</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E53" s="8" t="s">
-        <x:v>537</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F53" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G53" s="7" t="s">
-        <x:v>465</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B54" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C54" s="7" t="s">
-        <x:v>512</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D54" s="7" t="s">
-        <x:v>428</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E54" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F54" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G54" s="7" t="s">
-        <x:v>519</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B55" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C55" s="7" t="s">
-        <x:v>352</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D55" s="7" t="s">
-        <x:v>445</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="E55" s="8" t="s">
-        <x:v>537</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F55" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G55" s="7" t="s">
-        <x:v>83</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B56" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C56" s="7" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D56" s="7" t="s">
-        <x:v>471</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E56" s="8" t="s">
-        <x:v>422</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F56" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G56" s="7" t="s">
-        <x:v>438</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B57" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C57" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D57" s="7" t="s">
-        <x:v>470</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E57" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F57" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G57" s="7" t="s">
-        <x:v>405</x:v>
+        <x:v>387</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B58" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C58" s="7" t="s">
-        <x:v>64</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="D58" s="7" t="s">
-        <x:v>467</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E58" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F58" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G58" s="7" t="s">
-        <x:v>400</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B59" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C59" s="7" t="s">
-        <x:v>43</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D59" s="7" t="s">
-        <x:v>223</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E59" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F59" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G59" s="7" t="s">
-        <x:v>521</x:v>
+        <x:v>314</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B60" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C60" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="D60" s="7" t="s">
-        <x:v>351</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="E60" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F60" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G60" s="7" t="s">
-        <x:v>409</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B61" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C61" s="7" t="s">
-        <x:v>357</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D61" s="7" t="s">
-        <x:v>475</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E61" s="8" t="s">
-        <x:v>361</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F61" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G61" s="7" t="s">
-        <x:v>113</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B62" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C62" s="7" t="s">
-        <x:v>356</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="D62" s="7" t="s">
-        <x:v>108</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E62" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F62" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G62" s="7" t="s">
-        <x:v>264</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B63" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C63" s="7" t="s">
-        <x:v>350</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="D63" s="7" t="s">
-        <x:v>461</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E63" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F63" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G63" s="7" t="s">
-        <x:v>529</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B64" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C64" s="7" t="s">
-        <x:v>336</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D64" s="7" t="s">
-        <x:v>414</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E64" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F64" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G64" s="7" t="s">
-        <x:v>338</x:v>
+        <x:v>521</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B65" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C65" s="7" t="s">
-        <x:v>348</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="D65" s="7" t="s">
-        <x:v>416</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="E65" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F65" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G65" s="7" t="s">
-        <x:v>338</x:v>
+        <x:v>521</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B66" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C66" s="7" t="s">
-        <x:v>439</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D66" s="7" t="s">
-        <x:v>104</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E66" s="8" t="s">
-        <x:v>537</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F66" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G66" s="7" t="s">
-        <x:v>104</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B67" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C67" s="7" t="s">
-        <x:v>341</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="D67" s="7" t="s">
-        <x:v>430</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E67" s="8" t="s">
-        <x:v>422</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F67" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G67" s="7" t="s">
-        <x:v>499</x:v>
+        <x:v>346</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B68" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C68" s="7" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D68" s="7" t="s">
-        <x:v>103</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E68" s="8" t="s">
-        <x:v>364</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="F68" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G68" s="7" t="s">
-        <x:v>360</x:v>
+        <x:v>528</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B69" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C69" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D69" s="7" t="s">
-        <x:v>470</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E69" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F69" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G69" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B70" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C70" s="7" t="s">
-        <x:v>64</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="D70" s="7" t="s">
-        <x:v>467</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E70" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F70" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G70" s="7" t="s">
-        <x:v>415</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B71" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C71" s="7" t="s">
-        <x:v>363</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="D71" s="7" t="s">
-        <x:v>419</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E71" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F71" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G71" s="7" t="s">
-        <x:v>107</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B72" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C72" s="7" t="s">
-        <x:v>509</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="D72" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E72" s="8" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F72" s="8" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="G72" s="7" t="s">
         <x:v>523</x:v>
-      </x:c>
-      <x:c r="F72" s="8" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G72" s="7" t="s">
-        <x:v>365</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B73" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C73" s="7" t="s">
-        <x:v>43</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D73" s="7" t="s">
-        <x:v>223</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E73" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F73" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G73" s="7" t="s">
-        <x:v>495</x:v>
+        <x:v>344</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="5" t="s">
-        <x:v>563</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B74" s="7" t="s">
-        <x:v>440</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C74" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="D74" s="7" t="s">
-        <x:v>508</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E74" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F74" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G74" s="7" t="s">
-        <x:v>409</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="5" t="s">
-        <x:v>563</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B75" s="7" t="s">
-        <x:v>440</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C75" s="7" t="s">
-        <x:v>424</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="D75" s="7" t="s">
-        <x:v>353</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="E75" s="8" t="s">
-        <x:v>361</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F75" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G75" s="7" t="s">
-        <x:v>117</x:v>
+        <x:v>447</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="5" t="s">
-        <x:v>563</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B76" s="7" t="s">
-        <x:v>440</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C76" s="7" t="s">
-        <x:v>359</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="D76" s="7" t="s">
-        <x:v>420</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E76" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F76" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G76" s="7" t="s">
-        <x:v>503</x:v>
+        <x:v>341</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="5" t="s">
-        <x:v>563</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B77" s="7" t="s">
-        <x:v>440</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C77" s="7" t="s">
-        <x:v>350</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="D77" s="7" t="s">
-        <x:v>461</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E77" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F77" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G77" s="7" t="s">
-        <x:v>529</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="5" t="s">
-        <x:v>563</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B78" s="7" t="s">
-        <x:v>440</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C78" s="7" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D78" s="7" t="s">
-        <x:v>404</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="E78" s="8" t="s">
-        <x:v>364</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="F78" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G78" s="7" t="s">
-        <x:v>112</x:v>
+        <x:v>428</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="5" t="s">
-        <x:v>563</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B79" s="7" t="s">
-        <x:v>440</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C79" s="7" t="s">
-        <x:v>509</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="D79" s="7" t="s">
-        <x:v>100</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E79" s="8" t="s">
-        <x:v>523</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="F79" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G79" s="7" t="s">
-        <x:v>458</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="5" t="s">
-        <x:v>563</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B80" s="7" t="s">
-        <x:v>440</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C80" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D80" s="7" t="s">
-        <x:v>470</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E80" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F80" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G80" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="5" t="s">
-        <x:v>563</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B81" s="7" t="s">
-        <x:v>440</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C81" s="7" t="s">
-        <x:v>64</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="D81" s="7" t="s">
-        <x:v>467</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E81" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F81" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G81" s="7" t="s">
-        <x:v>373</x:v>
+        <x:v>543</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="5" t="s">
-        <x:v>563</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B82" s="7" t="s">
-        <x:v>440</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C82" s="7" t="s">
-        <x:v>43</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D82" s="7" t="s">
-        <x:v>223</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E82" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F82" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G82" s="7" t="s">
-        <x:v>375</x:v>
+        <x:v>542</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B83" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C83" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="D83" s="7" t="s">
-        <x:v>377</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="E83" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F83" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G83" s="7" t="s">
-        <x:v>409</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B84" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C84" s="7" t="s">
-        <x:v>85</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D84" s="7" t="s">
-        <x:v>89</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E84" s="8" t="s">
-        <x:v>361</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F84" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G84" s="7" t="s">
-        <x:v>118</x:v>
+        <x:v>448</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B85" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C85" s="7" t="s">
-        <x:v>429</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D85" s="7" t="s">
-        <x:v>378</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="E85" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F85" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G85" s="7" t="s">
-        <x:v>517</x:v>
+        <x:v>309</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B86" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C86" s="7" t="s">
-        <x:v>350</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="D86" s="7" t="s">
-        <x:v>461</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E86" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F86" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G86" s="7" t="s">
-        <x:v>529</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B87" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C87" s="7" t="s">
-        <x:v>367</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="D87" s="7" t="s">
-        <x:v>425</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E87" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F87" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G87" s="7" t="s">
-        <x:v>73</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B88" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C88" s="7" t="s">
-        <x:v>439</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D88" s="7" t="s">
-        <x:v>33</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E88" s="8" t="s">
-        <x:v>537</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F88" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G88" s="7" t="s">
-        <x:v>518</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B89" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C89" s="7" t="s">
-        <x:v>341</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="D89" s="7" t="s">
-        <x:v>371</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="E89" s="8" t="s">
-        <x:v>422</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F89" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G89" s="7" t="s">
-        <x:v>515</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B90" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C90" s="7" t="s">
-        <x:v>260</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D90" s="7" t="s">
-        <x:v>421</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="E90" s="8" t="s">
-        <x:v>422</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F90" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G90" s="7" t="s">
-        <x:v>372</x:v>
+        <x:v>546</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B91" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C91" s="7" t="s">
-        <x:v>496</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D91" s="7" t="s">
-        <x:v>427</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E91" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F91" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G91" s="7" t="s">
-        <x:v>458</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B92" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C92" s="7" t="s">
-        <x:v>263</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D92" s="7" t="s">
-        <x:v>106</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E92" s="8" t="s">
-        <x:v>366</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="F92" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G92" s="7" t="s">
-        <x:v>458</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B93" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C93" s="7" t="s">
-        <x:v>279</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D93" s="7" t="s">
-        <x:v>289</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="E93" s="8" t="s">
-        <x:v>498</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="F93" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G93" s="7" t="s">
-        <x:v>78</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B94" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C94" s="7" t="s">
-        <x:v>509</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="D94" s="7" t="s">
-        <x:v>100</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E94" s="8" t="s">
-        <x:v>523</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="F94" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G94" s="7" t="s">
-        <x:v>406</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B95" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C95" s="7" t="s">
-        <x:v>342</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D95" s="7" t="s">
-        <x:v>40</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E95" s="8" t="s">
-        <x:v>454</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F95" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G95" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B96" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C96" s="7" t="s">
-        <x:v>335</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="D96" s="7" t="s">
-        <x:v>473</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E96" s="8" t="s">
-        <x:v>454</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F96" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G96" s="7" t="s">
-        <x:v>288</x:v>
+        <x:v>458</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B97" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C97" s="7" t="s">
-        <x:v>293</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="D97" s="7" t="s">
-        <x:v>13</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="E97" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F97" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G97" s="7" t="s">
-        <x:v>497</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B98" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C98" s="7" t="s">
-        <x:v>500</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D98" s="7" t="s">
-        <x:v>426</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E98" s="8" t="s">
-        <x:v>537</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F98" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G98" s="7" t="s">
-        <x:v>247</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B99" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C99" s="7" t="s">
-        <x:v>262</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D99" s="7" t="s">
-        <x:v>295</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="E99" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F99" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G99" s="7" t="s">
-        <x:v>522</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B100" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C100" s="7" t="s">
-        <x:v>541</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="D100" s="7" t="s">
-        <x:v>290</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E100" s="8" t="s">
-        <x:v>540</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F100" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G100" s="7" t="s">
-        <x:v>261</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B101" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C101" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D101" s="7" t="s">
-        <x:v>470</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E101" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F101" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G101" s="7" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B102" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C102" s="7" t="s">
-        <x:v>64</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="D102" s="7" t="s">
-        <x:v>467</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E102" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F102" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G102" s="7" t="s">
-        <x:v>281</x:v>
+        <x:v>453</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="5" t="s">
-        <x:v>442</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B103" s="7" t="s">
-        <x:v>444</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C103" s="7" t="s">
-        <x:v>43</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D103" s="7" t="s">
-        <x:v>223</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E103" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F103" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G103" s="7" t="s">
-        <x:v>291</x:v>
+        <x:v>472</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B104" s="7" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C104" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="D104" s="7" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E104" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F104" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G104" s="7" t="s">
-        <x:v>409</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B105" s="7" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C105" s="7" t="s">
-        <x:v>350</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="D105" s="7" t="s">
-        <x:v>461</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E105" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F105" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G105" s="7" t="s">
-        <x:v>529</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B106" s="7" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C106" s="7" t="s">
-        <x:v>501</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="D106" s="7" t="s">
-        <x:v>292</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="E106" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F106" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G106" s="7" t="s">
-        <x:v>338</x:v>
+        <x:v>521</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B107" s="7" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C107" s="7" t="s">
-        <x:v>284</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="D107" s="7" t="s">
-        <x:v>102</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E107" s="8" t="s">
-        <x:v>280</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F107" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G107" s="7" t="s">
-        <x:v>269</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B108" s="7" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C108" s="7" t="s">
-        <x:v>282</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="D108" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E108" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F108" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G108" s="7" t="s">
-        <x:v>252</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B109" s="7" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C109" s="7" t="s">
-        <x:v>524</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="D109" s="7" t="s">
-        <x:v>111</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E109" s="8" t="s">
-        <x:v>526</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F109" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G109" s="7" t="s">
-        <x:v>255</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B110" s="7" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C110" s="7" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D110" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E110" s="8" t="s">
-        <x:v>361</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F110" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G110" s="7" t="s">
-        <x:v>505</x:v>
+        <x:v>342</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B111" s="7" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C111" s="7" t="s">
-        <x:v>294</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="D111" s="7" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E111" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F111" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G111" s="7" t="s">
-        <x:v>458</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B112" s="7" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C112" s="7" t="s">
-        <x:v>532</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D112" s="7" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E112" s="8" t="s">
-        <x:v>61</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F112" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G112" s="7" t="s">
-        <x:v>283</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B113" s="7" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C113" s="7" t="s">
-        <x:v>270</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D113" s="7" t="s">
-        <x:v>285</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="E113" s="8" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F113" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G113" s="7" t="s">
-        <x:v>286</x:v>
+        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:7">
       <x:c r="A114" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B114" s="7" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C114" s="7" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="D114" s="7" t="s">
         <x:v>451</x:v>
       </x:c>
-      <x:c r="C114" s="7" t="s">
-        <x:v>533</x:v>
-      </x:c>
-      <x:c r="D114" s="7" t="s">
-        <x:v>287</x:v>
-      </x:c>
       <x:c r="E114" s="8" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F114" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G114" s="7" t="s">
-        <x:v>296</x:v>
+        <x:v>474</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:7">
       <x:c r="A115" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B115" s="7" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C115" s="7" t="s">
-        <x:v>271</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D115" s="7" t="s">
-        <x:v>87</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E115" s="8" t="s">
-        <x:v>523</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="F115" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G115" s="7" t="s">
-        <x:v>80</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
       <x:c r="A116" s="5" t="s">
-        <x:v>441</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B116" s="7" t="s">
-        <x:v>451</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C116" s="7" t="s">
-        <x:v>547</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D116" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E116" s="8" t="s">
-        <x:v>422</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F116" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G116" s="7" t="s">
-        <x:v>275</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5103,8 +5106,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet4"/>
-  <x:dimension ref="A1:D145"/>
+  <x:sheetPr codeName="Sheet4" filterMode="1"/>
+  <x:dimension ref="A1:D141"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="13.765625" bestFit="1" customWidth="1"/>
@@ -5115,2036 +5118,1985 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" t="s">
-        <x:v>213</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>185</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>455</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>387</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" t="s">
-        <x:v>480</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>507</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C2" t="s">
-        <x:v>79</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D2" t="s">
-        <x:v>75</x:v>
+        <x:v>373</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" t="s">
-        <x:v>480</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>507</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C3" t="s">
-        <x:v>81</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D3" t="s">
-        <x:v>82</x:v>
+        <x:v>392</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" t="s">
-        <x:v>480</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>507</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C4" t="s">
-        <x:v>246</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D4" t="s">
-        <x:v>242</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" t="s">
-        <x:v>480</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>507</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>115</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D5" t="s">
-        <x:v>116</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" t="s">
-        <x:v>480</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>507</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>273</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D6" t="s">
-        <x:v>272</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" t="s">
-        <x:v>480</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>507</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>485</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>190</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" t="s">
-        <x:v>480</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>316</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>202</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="D8" t="s">
-        <x:v>202</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" t="s">
-        <x:v>480</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>316</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>205</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>205</x:v>
+        <x:v>401</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" t="s">
-        <x:v>480</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>219</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>196</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>187</x:v>
+        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" t="s">
-        <x:v>480</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>219</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>248</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D11" t="s">
-        <x:v>570</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" t="s">
-        <x:v>480</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>450</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" t="s">
-        <x:v>480</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>450</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>194</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>195</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" t="s">
-        <x:v>480</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>320</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>207</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>207</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" t="s">
-        <x:v>480</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>200</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>76</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D15" t="s">
-        <x:v>201</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" t="s">
-        <x:v>480</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>200</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>191</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="D16" t="s">
-        <x:v>191</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" t="s">
-        <x:v>480</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>209</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>274</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D17" t="s">
-        <x:v>571</x:v>
+        <x:v>421</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" t="s">
-        <x:v>480</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>209</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>276</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D18" t="s">
-        <x:v>572</x:v>
+        <x:v>576</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" t="s">
-        <x:v>480</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>209</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>28</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="D19" t="s">
-        <x:v>28</x:v>
+        <x:v>422</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" t="s">
-        <x:v>480</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>31</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>34</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D20" t="s">
-        <x:v>34</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" t="s">
-        <x:v>480</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>566</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>77</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D21" t="s">
-        <x:v>197</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" t="s">
-        <x:v>480</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>566</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>478</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D22" t="s">
-        <x:v>569</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" t="s">
-        <x:v>480</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>566</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>198</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D23" t="s">
-        <x:v>198</x:v>
+        <x:v>568</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" t="s">
-        <x:v>480</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>479</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>245</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D24" t="s">
-        <x:v>199</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B25" t="s">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="B25" t="s">
-        <x:v>479</x:v>
-      </x:c>
       <x:c r="C25" t="s">
-        <x:v>477</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D25" t="s">
-        <x:v>568</x:v>
+        <x:v>389</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" t="s">
-        <x:v>129</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>138</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>134</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D26" t="s">
-        <x:v>11</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" t="s">
-        <x:v>129</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>138</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>128</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D27" t="s">
-        <x:v>22</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" t="s">
-        <x:v>129</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>138</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>133</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="D28" t="s">
-        <x:v>23</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" t="s">
-        <x:v>129</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>138</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>516</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="D29" t="s">
-        <x:v>124</x:v>
+        <x:v>339</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" t="s">
-        <x:v>129</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>491</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>277</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D30" t="s">
-        <x:v>302</x:v>
+        <x:v>406</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" t="s">
-        <x:v>129</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>491</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>278</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D31" t="s">
-        <x:v>298</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" t="s">
-        <x:v>129</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>491</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>520</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="D32" t="s">
-        <x:v>506</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" t="s">
-        <x:v>129</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>303</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>484</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="D33" t="s">
-        <x:v>27</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" t="s">
-        <x:v>129</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>303</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>299</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="D34" t="s">
-        <x:v>55</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" t="s">
-        <x:v>129</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>303</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>131</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="D35" t="s">
-        <x:v>440</x:v>
+        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>26</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>147</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D36" t="s">
-        <x:v>140</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>26</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>304</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D37" t="s">
-        <x:v>313</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" t="s">
-        <x:v>121</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>380</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>132</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D38" t="s">
-        <x:v>137</x:v>
+        <x:v>419</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>380</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>120</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D39" t="s">
-        <x:v>136</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" t="s">
-        <x:v>121</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>380</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>152</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D40" t="s">
-        <x:v>126</x:v>
+        <x:v>393</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" t="s">
-        <x:v>121</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>380</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>141</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D41" t="s">
-        <x:v>122</x:v>
+        <x:v>396</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>380</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>123</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D42" t="s">
-        <x:v>149</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" t="s">
-        <x:v>121</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>380</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>148</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D43" t="s">
-        <x:v>130</x:v>
+        <x:v>402</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>380</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D44" t="s">
-        <x:v>145</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>380</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>150</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D45" t="s">
-        <x:v>135</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>507</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>139</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D46" t="s">
-        <x:v>151</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" t="s">
-        <x:v>121</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>507</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>318</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="D47" t="s">
-        <x:v>315</x:v>
+        <x:v>562</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" t="s">
-        <x:v>121</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>507</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>4</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D48" t="s">
-        <x:v>4</x:v>
+        <x:v>557</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>507</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>21</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="D49" t="s">
-        <x:v>21</x:v>
+        <x:v>412</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" t="s">
-        <x:v>121</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>507</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>158</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="D50" t="s">
-        <x:v>180</x:v>
+        <x:v>446</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" t="s">
-        <x:v>121</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>507</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>306</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D51" t="s">
-        <x:v>307</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B52" t="s">
-        <x:v>507</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>170</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="D52" t="s">
-        <x:v>176</x:v>
+        <x:v>358</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>507</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>239</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="D53" t="s">
-        <x:v>220</x:v>
+        <x:v>409</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>316</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>312</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D54" t="s">
-        <x:v>311</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" t="s">
-        <x:v>121</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>316</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>238</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="D55" t="s">
-        <x:v>231</x:v>
+        <x:v>365</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" t="s">
-        <x:v>121</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>316</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>228</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D56" t="s">
-        <x:v>235</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" t="s">
-        <x:v>121</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>316</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="D57" t="s">
-        <x:v>218</x:v>
+        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" t="s">
-        <x:v>121</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>316</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>402</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="D58" t="s">
-        <x:v>402</x:v>
+        <x:v>377</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>219</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>494</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D59" t="s">
-        <x:v>502</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>219</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>240</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="D60" t="s">
-        <x:v>433</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" t="s">
-        <x:v>121</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B61" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C61" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="D61" t="s">
         <x:v>219</x:v>
-      </x:c>
-      <x:c r="C61" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="D61" t="s">
-        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" t="s">
-        <x:v>121</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>219</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>431</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D62" t="s">
-        <x:v>446</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" t="s">
-        <x:v>121</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>450</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>86</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D63" t="s">
-        <x:v>237</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" t="s">
-        <x:v>121</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>450</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>162</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="D64" t="s">
-        <x:v>166</x:v>
+        <x:v>573</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" t="s">
-        <x:v>121</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>450</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>309</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D65" t="s">
-        <x:v>310</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:4">
       <x:c r="A66" t="s">
-        <x:v>121</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>450</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>319</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="D66" t="s">
-        <x:v>323</x:v>
+        <x:v>577</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:4">
       <x:c r="A67" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>450</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>314</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D67" t="s">
-        <x:v>325</x:v>
+        <x:v>426</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:4">
       <x:c r="A68" t="s">
-        <x:v>121</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>450</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>324</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D68" t="s">
-        <x:v>317</x:v>
+        <x:v>423</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:4">
       <x:c r="A69" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>450</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>513</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D69" t="s">
-        <x:v>504</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:4">
       <x:c r="A70" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>561</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>182</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="D70" t="s">
-        <x:v>171</x:v>
+        <x:v>459</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:4">
       <x:c r="A71" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>561</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>159</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="D71" t="s">
-        <x:v>177</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:4">
       <x:c r="A72" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>561</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>389</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D72" t="s">
-        <x:v>388</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:4">
       <x:c r="A73" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>561</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>156</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D73" t="s">
-        <x:v>169</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:4">
       <x:c r="A74" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>561</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>167</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="D74" t="s">
-        <x:v>167</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:4">
       <x:c r="A75" t="s">
-        <x:v>121</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>561</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>395</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D75" t="s">
-        <x:v>395</x:v>
+        <x:v>417</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:4">
       <x:c r="A76" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>561</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>488</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="D76" t="s">
-        <x:v>489</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:4">
       <x:c r="A77" t="s">
-        <x:v>121</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>320</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>322</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D77" t="s">
-        <x:v>321</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:4">
       <x:c r="A78" t="s">
-        <x:v>121</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>320</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>297</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D78" t="s">
-        <x:v>300</x:v>
+        <x:v>413</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:4">
       <x:c r="A79" t="s">
-        <x:v>121</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>320</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>163</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="D79" t="s">
-        <x:v>179</x:v>
+        <x:v>397</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:4">
       <x:c r="A80" t="s">
-        <x:v>121</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>320</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>164</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="D80" t="s">
-        <x:v>181</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:4">
       <x:c r="A81" t="s">
-        <x:v>121</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>320</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>168</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="D81" t="s">
-        <x:v>178</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:4">
       <x:c r="A82" t="s">
-        <x:v>121</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>320</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>390</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D82" t="s">
-        <x:v>35</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:4">
       <x:c r="A83" t="s">
-        <x:v>121</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>320</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>188</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="D83" t="s">
-        <x:v>157</x:v>
+        <x:v>405</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:4">
       <x:c r="A84" t="s">
-        <x:v>121</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>320</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D84" t="s">
-        <x:v>36</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:4">
       <x:c r="A85" t="s">
-        <x:v>121</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>320</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>153</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="D85" t="s">
-        <x:v>403</x:v>
+        <x:v>419</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:4">
       <x:c r="A86" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B86" t="s">
-        <x:v>173</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>392</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D86" t="s">
-        <x:v>32</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:4">
       <x:c r="A87" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>173</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>154</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D87" t="s">
-        <x:v>160</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:4">
       <x:c r="A88" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B88" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="C88" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D88" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B88" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="C88" t="s">
-        <x:v>487</x:v>
-      </x:c>
-      <x:c r="D88" t="s">
-        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:4">
       <x:c r="A89" t="s">
-        <x:v>121</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>173</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>165</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D89" t="s">
-        <x:v>174</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:4">
       <x:c r="A90" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>31</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>155</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D90" t="s">
-        <x:v>172</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:4">
       <x:c r="A91" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>31</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>183</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D91" t="s">
-        <x:v>192</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:4">
       <x:c r="A92" t="s">
-        <x:v>121</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>31</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>175</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D92" t="s">
-        <x:v>161</x:v>
+        <x:v>399</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:4">
       <x:c r="A93" t="s">
-        <x:v>121</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>189</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C93" t="s">
-        <x:v>206</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D93" t="s">
-        <x:v>204</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:4">
       <x:c r="A94" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>189</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C94" t="s">
-        <x:v>193</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="D94" t="s">
-        <x:v>210</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:4">
       <x:c r="A95" t="s">
-        <x:v>121</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>189</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C95" t="s">
-        <x:v>567</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D95" t="s">
-        <x:v>573</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:4">
       <x:c r="A96" t="s">
-        <x:v>121</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>30</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>45</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D96" t="s">
-        <x:v>50</x:v>
+        <x:v>421</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:4">
       <x:c r="A97" t="s">
-        <x:v>386</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>370</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>368</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D97" t="s">
-        <x:v>396</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:4">
       <x:c r="A98" t="s">
-        <x:v>386</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>370</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>376</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="D98" t="s">
-        <x:v>101</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:4">
       <x:c r="A99" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>370</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>514</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="D99" t="s">
-        <x:v>393</x:v>
+        <x:v>503</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:4">
       <x:c r="A100" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B100" t="s">
-        <x:v>370</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>56</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D100" t="s">
-        <x:v>398</x:v>
+        <x:v>384</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:4">
       <x:c r="A101" t="s">
-        <x:v>386</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B101" t="s">
-        <x:v>370</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>483</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="D101" t="s">
-        <x:v>383</x:v>
+        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:4">
       <x:c r="A102" t="s">
-        <x:v>386</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B102" t="s">
-        <x:v>370</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>385</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="D102" t="s">
-        <x:v>397</x:v>
+        <x:v>408</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:4">
       <x:c r="A103" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B103" t="s">
-        <x:v>370</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>374</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="D103" t="s">
-        <x:v>391</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:4">
       <x:c r="A104" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B104" t="s">
-        <x:v>369</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>561</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D104" t="s">
-        <x:v>562</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:4">
       <x:c r="A105" t="s">
-        <x:v>386</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B105" t="s">
-        <x:v>369</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>380</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="D105" t="s">
-        <x:v>110</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:4">
       <x:c r="A106" t="s">
-        <x:v>386</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B106" t="s">
-        <x:v>369</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>560</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="D106" t="s">
-        <x:v>559</x:v>
+        <x:v>367</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:4">
       <x:c r="A107" t="s">
-        <x:v>386</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B107" t="s">
-        <x:v>369</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>381</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D107" t="s">
-        <x:v>379</x:v>
+        <x:v>463</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:4">
       <x:c r="A108" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B108" t="s">
-        <x:v>369</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>490</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D108" t="s">
-        <x:v>511</x:v>
+        <x:v>493</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:4">
       <x:c r="A109" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B109" t="s">
-        <x:v>369</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>492</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D109" t="s">
-        <x:v>493</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:4">
       <x:c r="A110" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B110" t="s">
-        <x:v>369</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>555</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="D110" t="s">
-        <x:v>549</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:4">
       <x:c r="A111" t="s">
-        <x:v>386</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B111" t="s">
-        <x:v>369</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>481</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="D111" t="s">
-        <x:v>482</x:v>
+        <x:v>558</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:4">
       <x:c r="A112" t="s">
-        <x:v>386</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B112" t="s">
-        <x:v>552</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>432</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D112" t="s">
-        <x:v>47</x:v>
+        <x:v>363</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:4">
       <x:c r="A113" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B113" t="s">
-        <x:v>552</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C113" t="s">
-        <x:v>550</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D113" t="s">
-        <x:v>18</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:4">
       <x:c r="A114" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B114" t="s">
-        <x:v>552</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>382</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="D114" t="s">
-        <x:v>1</x:v>
+        <x:v>336</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:4">
       <x:c r="A115" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B115" t="s">
-        <x:v>552</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C115" t="s">
-        <x:v>384</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D115" t="s">
-        <x:v>401</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:4">
       <x:c r="A116" t="s">
-        <x:v>386</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B116" t="s">
-        <x:v>552</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C116" t="s">
-        <x:v>84</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="D116" t="s">
-        <x:v>12</x:v>
+        <x:v>415</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:4">
       <x:c r="A117" t="s">
-        <x:v>386</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B117" t="s">
-        <x:v>552</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="C117" t="s">
-        <x:v>510</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D117" t="s">
-        <x:v>17</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:4">
       <x:c r="A118" t="s">
-        <x:v>386</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B118" t="s">
-        <x:v>552</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>558</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D118" t="s">
-        <x:v>399</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:4">
       <x:c r="A119" t="s">
-        <x:v>386</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B119" t="s">
-        <x:v>144</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>551</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D119" t="s">
-        <x:v>7</x:v>
+        <x:v>416</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:4">
       <x:c r="A120" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B120" t="s">
-        <x:v>144</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>67</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D120" t="s">
-        <x:v>19</x:v>
+        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:4">
       <x:c r="A121" t="s">
-        <x:v>386</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B121" t="s">
-        <x:v>144</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>143</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D121" t="s">
-        <x:v>3</x:v>
+        <x:v>414</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:4">
       <x:c r="A122" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B122" t="s">
-        <x:v>138</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>125</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D122" t="s">
-        <x:v>394</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:4">
       <x:c r="A123" t="s">
-        <x:v>386</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B123" t="s">
-        <x:v>138</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C123" t="s">
-        <x:v>146</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="D123" t="s">
-        <x:v>10</x:v>
+        <x:v>383</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:4">
       <x:c r="A124" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B124" t="s">
-        <x:v>138</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="C124" t="s">
-        <x:v>301</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D124" t="s">
-        <x:v>9</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:4">
       <x:c r="A125" t="s">
-        <x:v>386</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B125" t="s">
-        <x:v>138</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C125" t="s">
-        <x:v>142</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="D125" t="s">
-        <x:v>20</x:v>
+        <x:v>572</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:4">
       <x:c r="A126" t="s">
-        <x:v>299</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B126" t="s">
-        <x:v>138</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="C126" t="s">
-        <x:v>232</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D126" t="s">
-        <x:v>5</x:v>
+        <x:v>398</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:4">
       <x:c r="A127" t="s">
-        <x:v>299</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B127" t="s">
-        <x:v>138</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C127" t="s">
-        <x:v>546</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D127" t="s">
-        <x:v>236</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:4">
       <x:c r="A128" t="s">
-        <x:v>299</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B128" t="s">
-        <x:v>138</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C128" t="s">
-        <x:v>576</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D128" t="s">
-        <x:v>241</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:4">
       <x:c r="A129" t="s">
-        <x:v>299</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B129" t="s">
-        <x:v>138</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C129" t="s">
-        <x:v>575</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D129" t="s">
-        <x:v>25</x:v>
+        <x:v>391</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:4">
       <x:c r="A130" t="s">
-        <x:v>131</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B130" t="s">
-        <x:v>138</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C130" t="s">
-        <x:v>232</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D130" t="s">
-        <x:v>5</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:4">
       <x:c r="A131" t="s">
-        <x:v>131</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B131" t="s">
-        <x:v>138</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C131" t="s">
-        <x:v>546</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="D131" t="s">
-        <x:v>236</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:4">
       <x:c r="A132" t="s">
-        <x:v>131</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B132" t="s">
-        <x:v>138</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="C132" t="s">
-        <x:v>576</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D132" t="s">
-        <x:v>241</x:v>
+        <x:v>362</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:4">
       <x:c r="A133" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B133" t="s">
-        <x:v>138</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C133" t="s">
-        <x:v>575</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D133" t="s">
-        <x:v>25</x:v>
+        <x:v>411</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:4">
       <x:c r="A134" t="s">
-        <x:v>221</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B134" t="s">
-        <x:v>138</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C134" t="s">
-        <x:v>224</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="D134" t="s">
-        <x:v>15</x:v>
+        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:4">
       <x:c r="A135" t="s">
-        <x:v>221</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B135" t="s">
-        <x:v>138</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C135" t="s">
-        <x:v>266</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D135" t="s">
-        <x:v>230</x:v>
+        <x:v>403</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:4">
       <x:c r="A136" t="s">
-        <x:v>221</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B136" t="s">
-        <x:v>138</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C136" t="s">
-        <x:v>578</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="D136" t="s">
-        <x:v>222</x:v>
+        <x:v>477</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:4">
       <x:c r="A137" t="s">
-        <x:v>221</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B137" t="s">
-        <x:v>138</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C137" t="s">
-        <x:v>226</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="D137" t="s">
-        <x:v>8</x:v>
+        <x:v>489</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:4">
       <x:c r="A138" t="s">
-        <x:v>221</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B138" t="s">
-        <x:v>138</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C138" t="s">
-        <x:v>580</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D138" t="s">
-        <x:v>24</x:v>
+        <x:v>492</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:4">
       <x:c r="A139" t="s">
-        <x:v>221</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B139" t="s">
-        <x:v>579</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C139" t="s">
-        <x:v>6</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="D139" t="s">
-        <x:v>0</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:4">
       <x:c r="A140" t="s">
-        <x:v>221</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B140" t="s">
-        <x:v>579</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C140" t="s">
-        <x:v>233</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="D140" t="s">
-        <x:v>14</x:v>
+        <x:v>482</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:4">
       <x:c r="A141" t="s">
-        <x:v>221</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B141" t="s">
-        <x:v>579</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C141" t="s">
-        <x:v>229</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D141" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="142" spans="1:4">
-      <x:c r="A142" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="B142" t="s">
-        <x:v>577</x:v>
-      </x:c>
-      <x:c r="C142" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="D142" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="143" spans="1:4">
-      <x:c r="A143" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="B143" t="s">
-        <x:v>577</x:v>
-      </x:c>
-      <x:c r="C143" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="D143" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="144" spans="1:4">
-      <x:c r="A144" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="B144" t="s">
-        <x:v>577</x:v>
-      </x:c>
-      <x:c r="C144" t="s">
-        <x:v>574</x:v>
-      </x:c>
-      <x:c r="D144" t="s">
-        <x:v>217</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" spans="1:4">
-      <x:c r="A145" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="B145" t="s">
-        <x:v>577</x:v>
-      </x:c>
-      <x:c r="C145" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="D145" t="s">
-        <x:v>8</x:v>
+        <x:v>379</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:autoFilter ref="A1:D1">
+    <x:sortState columnSort="0" caseSensitive="0" ref="A2:D145">
+      <x:sortCondition descending="0" sortBy="value" ref="C2:C145"/>
+    </x:sortState>
+  </x:autoFilter>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
